--- a/Honda_Logi/Excel_Format/機種摘要モジュール一覧.xlsx
+++ b/Honda_Logi/Excel_Format/機種摘要モジュール一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06DDA15-3ADA-4244-96EB-55DF5D7A48AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7407A8-D3EA-484B-8B31-6A6F2E78547D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{802AD8BF-0384-4F9D-8945-7A36CE6A5C92}"/>
+    <workbookView xWindow="30810" yWindow="3765" windowWidth="21600" windowHeight="12735" xr2:uid="{802AD8BF-0384-4F9D-8945-7A36CE6A5C92}"/>
   </bookViews>
   <sheets>
     <sheet name="機種摘要モジュール一覧" sheetId="1" r:id="rId1"/>
@@ -218,7 +218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -240,53 +240,62 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -666,30 +675,29 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="1.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="3.625" style="1" customWidth="1"/>
-    <col min="6" max="10" width="6.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="3.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="3.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="3.625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="3.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="8.625" style="3" customWidth="1"/>
-    <col min="22" max="22" width="3.625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="8.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="3.625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="8.625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="3.625" style="1" customWidth="1"/>
-    <col min="27" max="28" width="9" style="1"/>
-    <col min="29" max="29" width="9" style="15"/>
-    <col min="30" max="30" width="17.375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="6.625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="3.625" style="7" customWidth="1"/>
+    <col min="6" max="10" width="6.625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="8.625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="3.625" style="19" customWidth="1"/>
+    <col min="13" max="13" width="8.625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="3.625" style="21" customWidth="1"/>
+    <col min="15" max="15" width="8.625" style="11" customWidth="1"/>
+    <col min="16" max="16" width="3.625" style="19" customWidth="1"/>
+    <col min="17" max="17" width="8.625" style="17" customWidth="1"/>
+    <col min="18" max="18" width="3.625" style="19" customWidth="1"/>
+    <col min="19" max="19" width="8.625" style="7" customWidth="1"/>
+    <col min="20" max="20" width="3.625" style="19" customWidth="1"/>
+    <col min="21" max="21" width="8.625" style="11" customWidth="1"/>
+    <col min="22" max="22" width="3.625" style="19" customWidth="1"/>
+    <col min="23" max="23" width="8.625" style="7" customWidth="1"/>
+    <col min="24" max="24" width="3.625" style="24" customWidth="1"/>
+    <col min="25" max="25" width="8.625" style="7" customWidth="1"/>
+    <col min="26" max="26" width="3.625" style="19" customWidth="1"/>
+    <col min="27" max="29" width="9" style="1"/>
+    <col min="30" max="30" width="17.375" style="5" bestFit="1" customWidth="1"/>
     <col min="31" max="258" width="9" style="1"/>
     <col min="259" max="259" width="1.875" style="1" customWidth="1"/>
     <col min="260" max="260" width="5" style="1" customWidth="1"/>
@@ -1957,6 +1965,14 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
       <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1964,30 +1980,60 @@
       <c r="M1" s="3"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="R1" s="1"/>
       <c r="S1" s="3"/>
+      <c r="T1" s="1"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
       <c r="W1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
       <c r="AB1" s="5"/>
-      <c r="AD1" s="15"/>
+      <c r="AD1" s="1"/>
     </row>
     <row r="2" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
       <c r="X2" s="2"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2052,596 +2098,604 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I4" s="18"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="20"/>
-    </row>
-    <row r="5" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="20"/>
-    </row>
-    <row r="6" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I6" s="18"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="20"/>
-    </row>
-    <row r="7" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
-      <c r="V7" s="21"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="20"/>
-    </row>
-    <row r="8" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I8" s="18"/>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="20"/>
-    </row>
-    <row r="9" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="20"/>
-    </row>
-    <row r="10" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="18"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="20"/>
-    </row>
-    <row r="11" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="20"/>
-    </row>
-    <row r="12" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I12" s="18"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="20"/>
-    </row>
-    <row r="13" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="20"/>
-    </row>
-    <row r="14" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I14" s="18"/>
-      <c r="AC14" s="19"/>
-      <c r="AD14" s="20"/>
-    </row>
-    <row r="15" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="20"/>
-    </row>
-    <row r="16" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I16" s="18"/>
-      <c r="AC16" s="19"/>
-      <c r="AD16" s="20"/>
-    </row>
-    <row r="17" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="20"/>
-    </row>
-    <row r="18" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="I18" s="18"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="20"/>
-    </row>
-    <row r="19" spans="2:30" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="20"/>
-    </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="G20" s="3"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
-    </row>
-    <row r="22" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="G22" s="3"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
-    </row>
-    <row r="24" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="G24" s="3"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="11"/>
-      <c r="Q24" s="10"/>
-    </row>
-    <row r="25" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
-    </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="G26" s="3"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="11"/>
-    </row>
-    <row r="27" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
-    </row>
-    <row r="28" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="G28" s="3"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="11"/>
-      <c r="Q28" s="10"/>
-    </row>
-    <row r="29" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="7"/>
-    </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="G30" s="3"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="11"/>
-    </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="7"/>
-    </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="G32" s="3"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="11"/>
+    <row r="4" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="I4" s="8"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="X4" s="19"/>
+    </row>
+    <row r="5" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="20"/>
+    </row>
+    <row r="6" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="I6" s="8"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="X6" s="19"/>
+    </row>
+    <row r="7" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="20"/>
+    </row>
+    <row r="8" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="I8" s="8"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="X8" s="19"/>
+    </row>
+    <row r="9" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="I10" s="8"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="X10" s="19"/>
+    </row>
+    <row r="11" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="20"/>
+    </row>
+    <row r="12" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="I12" s="8"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="X12" s="19"/>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="20"/>
+    </row>
+    <row r="14" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="I14" s="8"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="X14" s="19"/>
+    </row>
+    <row r="15" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="20"/>
+    </row>
+    <row r="16" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="I16" s="8"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="X16" s="19"/>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="20"/>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="I18" s="8"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="X18" s="19"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="20"/>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="13"/>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="20"/>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="G22" s="11"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="13"/>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="20"/>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="G24" s="11"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="13"/>
+      <c r="Q24" s="12"/>
+    </row>
+    <row r="25" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="20"/>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="G26" s="11"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="13"/>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="20"/>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="G28" s="11"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="13"/>
+      <c r="Q28" s="12"/>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="20"/>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="G30" s="11"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="20"/>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="G32" s="11"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="7"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="20"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="G34" s="2"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="11"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="7"/>
-      <c r="Z35" s="7"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="20"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="G36" s="3"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="13"/>
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="9"/>
-      <c r="Y37" s="7"/>
-      <c r="Z37" s="7"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="20"/>
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="G38" s="3"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="11"/>
-      <c r="X38" s="1"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="13"/>
+      <c r="X38" s="19"/>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="7"/>
-      <c r="X39" s="1"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="14"/>
+      <c r="P39" s="20"/>
+      <c r="X39" s="19"/>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="X40" s="1"/>
+      <c r="X40" s="19"/>
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.4">
-      <c r="X41" s="1"/>
+      <c r="X41" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
